--- a/results 5 workers/Results 5 workers.xlsx
+++ b/results 5 workers/Results 5 workers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumentumok_2026\PS\Revision\Logs Results revision\results 5 workers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumentumok_2026\PS\Revision\For resubmit\Repository\results 5 workers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F178EF-01FF-4348-881C-F35C3375082E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F769B07-5993-43B6-BBB8-DF74924F6AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1301,7 +1301,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4335,15 +4335,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="V54:W54"/>
-    <mergeCell ref="V56:W56"/>
-    <mergeCell ref="V57:W57"/>
-    <mergeCell ref="S61:T61"/>
-    <mergeCell ref="V47:W47"/>
-    <mergeCell ref="V48:W48"/>
-    <mergeCell ref="V50:W50"/>
-    <mergeCell ref="V51:W51"/>
-    <mergeCell ref="V53:W53"/>
     <mergeCell ref="C53:D53"/>
     <mergeCell ref="F53:G53"/>
     <mergeCell ref="F39:G39"/>
@@ -4354,6 +4345,15 @@
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="F49:G49"/>
+    <mergeCell ref="V54:W54"/>
+    <mergeCell ref="V56:W56"/>
+    <mergeCell ref="V57:W57"/>
+    <mergeCell ref="S61:T61"/>
+    <mergeCell ref="V47:W47"/>
+    <mergeCell ref="V48:W48"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="V53:W53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
